--- a/06_Testing_Results_and_Evaluation/Test_Cases_and_Results.xlsx
+++ b/06_Testing_Results_and_Evaluation/Test_Cases_and_Results.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ctutrainingsolutionspt-my.sharepoint.com/personal/lusukama_selemani_ctutraining_co_za/Documents/Documents/POES-LUSUKAMA/Research-2026/Capstone_Project_Pack_with_CTU_Logo/Capstone_Project_Pack/06_Testing_Results_and_Evaluation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sihle Kayise\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{CEC173AF-77E1-48A0-B51B-C576C11049EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76BDD8FA-5754-45B1-8952-8D827E804FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tracker!$A$3:$L$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tracker!$A$3:$L$100</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="120">
   <si>
     <t>SOFTWARE TEST CASES &amp; RESULTS</t>
   </si>
@@ -62,13 +62,334 @@
   </si>
   <si>
     <t>Evidence</t>
+  </si>
+  <si>
+    <t>TC-001</t>
+  </si>
+  <si>
+    <t>REQ-001</t>
+  </si>
+  <si>
+    <t>Student Login</t>
+  </si>
+  <si>
+    <t>Student account exists and system is online</t>
+  </si>
+  <si>
+    <t>1. Open login page. 2. Enter valid student credentials. 3. Click Login.</t>
+  </si>
+  <si>
+    <t>Valid student username and password</t>
+  </si>
+  <si>
+    <t>Student should successfully log in and be redirected to dashboard.</t>
+  </si>
+  <si>
+    <t>Student logged in successfully and dashboard displayed.</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Sihle Kayise</t>
+  </si>
+  <si>
+    <t>TC-002</t>
+  </si>
+  <si>
+    <t>REQ-002</t>
+  </si>
+  <si>
+    <t>Student Dashboard</t>
+  </si>
+  <si>
+    <t>Student is logged in</t>
+  </si>
+  <si>
+    <t>1. Log in as student. 2. View dashboard.</t>
+  </si>
+  <si>
+    <t>Student account</t>
+  </si>
+  <si>
+    <t>Dashboard should load and all functions should be accessible.</t>
+  </si>
+  <si>
+    <t>Dashboard appeared and worked correctly.</t>
+  </si>
+  <si>
+    <t>TC-003</t>
+  </si>
+  <si>
+    <t>REQ-003</t>
+  </si>
+  <si>
+    <t>View Existing Logbook Entry</t>
+  </si>
+  <si>
+    <t>Student has an existing logbook entry</t>
+  </si>
+  <si>
+    <t>1. Open dashboard. 2. Click on an existing entry date.</t>
+  </si>
+  <si>
+    <t>Existing logbook entry</t>
+  </si>
+  <si>
+    <t>Selected entry details should open successfully.</t>
+  </si>
+  <si>
+    <t>Entry displayed successfully.</t>
+  </si>
+  <si>
+    <t>TC-004</t>
+  </si>
+  <si>
+    <t>REQ-004</t>
+  </si>
+  <si>
+    <t>Back to Logbook Navigation</t>
+  </si>
+  <si>
+    <t>Student is viewing a logbook entry</t>
+  </si>
+  <si>
+    <t>1. Open an entry. 2. Click "Back to Logbook".</t>
+  </si>
+  <si>
+    <t>Existing entry</t>
+  </si>
+  <si>
+    <t>User should be redirected to Logbook Dashboard.</t>
+  </si>
+  <si>
+    <t>Redirected successfully to Logbook Dashboard.</t>
+  </si>
+  <si>
+    <t>TC-005</t>
+  </si>
+  <si>
+    <t>REQ-005</t>
+  </si>
+  <si>
+    <t>Create New Logbook Entry</t>
+  </si>
+  <si>
+    <t>1. Click "New Entry". 2. Complete all fields. 3. Submit entry.</t>
+  </si>
+  <si>
+    <t>Logbook information (date, activities, hours worked, comments)</t>
+  </si>
+  <si>
+    <t>New entry form should open and accept user input.</t>
+  </si>
+  <si>
+    <t>New entry created successfully and all fields were functional.</t>
+  </si>
+  <si>
+    <t>TC-006</t>
+  </si>
+  <si>
+    <t>REQ-006</t>
+  </si>
+  <si>
+    <t>Save Logbook Entry</t>
+  </si>
+  <si>
+    <t>New logbook entry has been completed</t>
+  </si>
+  <si>
+    <t>1. Fill in entry form. 2. Click "Save Entry".</t>
+  </si>
+  <si>
+    <t>Completed logbook details</t>
+  </si>
+  <si>
+    <t>Entry should save successfully and appear on dashboard.</t>
+  </si>
+  <si>
+    <t>Entry saved successfully and displayed on logbook dashboard.</t>
+  </si>
+  <si>
+    <t>TC-007</t>
+  </si>
+  <si>
+    <t>REQ-007</t>
+  </si>
+  <si>
+    <t>Student Sign Out</t>
+  </si>
+  <si>
+    <t>1. Click "Sign Out".</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>User should be logged out and redirected to login page.</t>
+  </si>
+  <si>
+    <t>Redirected to login page successfully.</t>
+  </si>
+  <si>
+    <t>TC-008</t>
+  </si>
+  <si>
+    <t>REQ-008</t>
+  </si>
+  <si>
+    <t>Coordinator Login</t>
+  </si>
+  <si>
+    <t>Coordinator account exists</t>
+  </si>
+  <si>
+    <t>1. Open login page. 2. Enter valid coordinator credentials. 3. Click Login.</t>
+  </si>
+  <si>
+    <t>Valid coordinator username and password</t>
+  </si>
+  <si>
+    <t>Coordinator should successfully log in.</t>
+  </si>
+  <si>
+    <t>Coordinator signed in successfully.</t>
+  </si>
+  <si>
+    <t>TC-009</t>
+  </si>
+  <si>
+    <t>REQ-009</t>
+  </si>
+  <si>
+    <t>Coordinator Dashboard</t>
+  </si>
+  <si>
+    <t>Coordinator is logged in</t>
+  </si>
+  <si>
+    <t>1. Log in as coordinator. 2. View dashboard.</t>
+  </si>
+  <si>
+    <t>Uploaded student logbook entries</t>
+  </si>
+  <si>
+    <t>Dashboard should display students who submitted entries.</t>
+  </si>
+  <si>
+    <t>Submitted student entries were visible.</t>
+  </si>
+  <si>
+    <t>TC-010</t>
+  </si>
+  <si>
+    <t>REQ-010</t>
+  </si>
+  <si>
+    <t>Coordinator Sign Out</t>
+  </si>
+  <si>
+    <t>User should be redirected to login page.</t>
+  </si>
+  <si>
+    <t>Redirected successfully to login page.</t>
+  </si>
+  <si>
+    <t>TC-011</t>
+  </si>
+  <si>
+    <t>TC-012</t>
+  </si>
+  <si>
+    <t>REQ-012</t>
+  </si>
+  <si>
+    <t>Student Login with Invalid Credentials</t>
+  </si>
+  <si>
+    <t>Student login page is accessible</t>
+  </si>
+  <si>
+    <t>1. Open login page. 2. Enter invalid username and/or password. 3. Click Login.</t>
+  </si>
+  <si>
+    <t>Invalid username/password</t>
+  </si>
+  <si>
+    <t>System should display an error message and deny access.</t>
+  </si>
+  <si>
+    <t>Error message displayed and login was unsuccessful.</t>
+  </si>
+  <si>
+    <t>TC-013</t>
+  </si>
+  <si>
+    <t>TC-014</t>
+  </si>
+  <si>
+    <t>REQ-014</t>
+  </si>
+  <si>
+    <t>Save Logbook Entry with Required Fields Empty</t>
+  </si>
+  <si>
+    <t>Student is logged in and on the New Entry page</t>
+  </si>
+  <si>
+    <t>1. Click "New Entry". 2. Leave one or more required fields blank. 3. Click "Save Entry".</t>
+  </si>
+  <si>
+    <t>Incomplete logbook entry</t>
+  </si>
+  <si>
+    <t>System should validate input and prevent saving until all required fields are completed.</t>
+  </si>
+  <si>
+    <t>Validation message displayed and entry was not saved.</t>
+  </si>
+  <si>
+    <t>REQ-015</t>
+  </si>
+  <si>
+    <t>Coordinator Login with Invalid Credentials</t>
+  </si>
+  <si>
+    <t>Coordinator login page is accessible</t>
+  </si>
+  <si>
+    <t>1. Enter incorrect login credentials. 2. Click Login.</t>
+  </si>
+  <si>
+    <t>Invalid coordinator username/password</t>
+  </si>
+  <si>
+    <t>REQ-017</t>
+  </si>
+  <si>
+    <t>Verify Saved Data After Logout and Login</t>
+  </si>
+  <si>
+    <t>Student has previously saved a logbook entry</t>
+  </si>
+  <si>
+    <t>1. Create and save a logbook entry. 2. Sign out. 3. Sign back in. 4. Open the logbook dashboard.</t>
+  </si>
+  <si>
+    <t>Previously saved logbook entry</t>
+  </si>
+  <si>
+    <t>Saved entry should still be available on the dashboard.</t>
+  </si>
+  <si>
+    <t>Saved entry remained visible after logging back in.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -86,6 +407,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -106,7 +433,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -132,17 +459,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFE6E6E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFE6E6E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFE6E6E6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFE6E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -448,8 +796,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L50"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -464,23 +812,23 @@
     <col min="12" max="12" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+    </row>
+    <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -518,203 +866,510 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="4">
+        <v>46317</v>
+      </c>
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" spans="1:12" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="4">
+        <v>46317</v>
+      </c>
+      <c r="L5" s="3"/>
+    </row>
+    <row r="6" spans="1:12" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="4">
+        <v>46317</v>
+      </c>
+      <c r="L6" s="3"/>
+    </row>
+    <row r="7" spans="1:12" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="4">
+        <v>46317</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="4">
+        <v>46317</v>
+      </c>
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="4">
+        <v>46317</v>
+      </c>
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="4">
+        <v>46317</v>
+      </c>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="4">
+        <v>46317</v>
+      </c>
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" s="4">
+        <v>46317</v>
+      </c>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="4">
+        <v>46317</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="4">
+        <v>46317</v>
+      </c>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="4">
+        <v>46317</v>
+      </c>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" s="4">
+        <v>46317</v>
+      </c>
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="1:12" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" s="4">
+        <v>46317</v>
+      </c>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -728,7 +1383,7 @@
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -742,7 +1397,7 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -756,7 +1411,7 @@
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -770,7 +1425,7 @@
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -784,7 +1439,7 @@
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -798,7 +1453,7 @@
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -812,7 +1467,7 @@
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -826,7 +1481,7 @@
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -840,7 +1495,7 @@
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -854,7 +1509,7 @@
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -868,7 +1523,7 @@
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -882,7 +1537,7 @@
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -896,7 +1551,7 @@
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -910,7 +1565,7 @@
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -924,7 +1579,7 @@
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -938,7 +1593,7 @@
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -952,7 +1607,7 @@
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -966,7 +1621,7 @@
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -980,7 +1635,7 @@
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -994,7 +1649,7 @@
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -1008,7 +1663,7 @@
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -1022,7 +1677,7 @@
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -1036,7 +1691,7 @@
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -1050,7 +1705,7 @@
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -1064,7 +1719,7 @@
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -1078,7 +1733,7 @@
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -1092,7 +1747,7 @@
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -1106,7 +1761,7 @@
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -1120,7 +1775,7 @@
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -1134,7 +1789,7 @@
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -1148,7 +1803,7 @@
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -1162,7 +1817,7 @@
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -1176,55 +1831,13 @@
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
-      <c r="L51" s="2"/>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-      <c r="L52" s="2"/>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-      <c r="L53" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:L103" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:L100" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="I4:I53" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I18:I50" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Not Run,Pass,Fail,Blocked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/06_Testing_Results_and_Evaluation/Test_Cases_and_Results.xlsx
+++ b/06_Testing_Results_and_Evaluation/Test_Cases_and_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gedion\Desktop\TrackWIL\06_Testing_Results_and_Evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFE0BAB-9137-43A7-B857-37609A1E3ECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E414B189-A04D-4874-A162-90D5F2722647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,8 @@
     <sheet name="Tracker" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tracker!$A$3:$L$100</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Tracker!$A$1:$L$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tracker!$A$3:$L$126</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Tracker!$A$1:$L$84</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Tracker!$3:$3</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="597">
   <si>
     <t>SOFTWARE TEST CASES &amp; RESULTS</t>
   </si>
@@ -567,12 +567,6 @@
     <t>Coordinator session</t>
   </si>
   <si>
-    <t>Redirected to /coordinator; logbook not shown.</t>
-  </si>
-  <si>
-    <t>status 307; redirected to /coordinator: true</t>
-  </si>
-  <si>
     <t>TC-119</t>
   </si>
   <si>
@@ -588,12 +582,6 @@
     <t>Student session</t>
   </si>
   <si>
-    <t>Redirected to /student; dashboard not shown.</t>
-  </si>
-  <si>
-    <t>status 307; redirected to /student: true</t>
-  </si>
-  <si>
     <t>TC-120</t>
   </si>
   <si>
@@ -648,12 +636,6 @@
     <t>Forged cookies</t>
   </si>
   <si>
-    <t>Both rejected; dashboard not shown.</t>
-  </si>
-  <si>
-    <t>unsigned 'coordinator-1' -&gt; dashboard shown: false; another user's signature -&gt; dashboard shown: false</t>
-  </si>
-  <si>
     <t>TC-122</t>
   </si>
   <si>
@@ -1002,15 +984,9 @@
     <t>TC-138</t>
   </si>
   <si>
-    <t>Logbook view</t>
-  </si>
-  <si>
     <t>Sihle's entries</t>
   </si>
   <si>
-    <t>Statuses shown; 'X of 200 verified hours completed' correct.</t>
-  </si>
-  <si>
     <t>expected "12.5 of 200 verified hours"; statuses shown: Draft, Pending verification, Verified</t>
   </si>
   <si>
@@ -1104,18 +1080,9 @@
     <t>Fresh copy of schema.sql</t>
   </si>
   <si>
-    <t>1. Insert six kinds of invalid rows.</t>
-  </si>
-  <si>
-    <t>Hours 30, bad status, missing student, bad role, duplicate email, token without decision</t>
-  </si>
-  <si>
     <t>Every insert rejected by a constraint.</t>
   </si>
   <si>
-    <t>hours = 30: rejected (CHECK constraint failed); unknown status: rejected (CHECK constraint failed); entry for missing student: rejected (FOREIGN KEY constraint failed); unknown role: rejected (CHECK constraint failed); duplicate email (case): rejected (UNIQUE constraint failed); token used without decision: rejected (CHECK constraint failed)</t>
-  </si>
-  <si>
     <t>TC-144</t>
   </si>
   <si>
@@ -1128,18 +1095,6 @@
     <t>Demo data loaded</t>
   </si>
   <si>
-    <t>1. Request five pages 10 times each. 2. Time one entry creation.</t>
-  </si>
-  <si>
-    <t>/, /student, /student/entries/new, /coordinator, /verify/&lt;token&gt;</t>
-  </si>
-  <si>
-    <t>Every response under 2 seconds.</t>
-  </si>
-  <si>
-    <t>/ avg 3 ms, max 4 ms; /student avg 5 ms, max 9 ms; /student/entries/new avg 4 ms, max 5 ms; /coordinator avg 4 ms, max 6 ms; /verify/&lt;token&gt; avg 4 ms, max 5 ms; create entry 20 ms</t>
-  </si>
-  <si>
     <t>TC-145</t>
   </si>
   <si>
@@ -1242,9 +1197,6 @@
     <t>Only synthetic data and team members' own names; no staff or other students' personal data.</t>
   </si>
   <si>
-    <t>Seed data contains only the four team members, a synthetic coordinator and a synthetic lecturer, and invented entries; no other personal data is stored.</t>
-  </si>
-  <si>
     <t>TC-149</t>
   </si>
   <si>
@@ -1276,6 +1228,594 @@
   </si>
   <si>
     <t>Ethical Clearance Confirmation</t>
+  </si>
+  <si>
+    <t>TC-150</t>
+  </si>
+  <si>
+    <t>FR-15</t>
+  </si>
+  <si>
+    <t>Add a WIL placement</t>
+  </si>
+  <si>
+    <t>Signed in as a new student</t>
+  </si>
+  <si>
+    <t>1. Send the add-placement form.</t>
+  </si>
+  <si>
+    <t>WIL 1, Test Host Company, 320 hours, 2026-10-01</t>
+  </si>
+  <si>
+    <t>Placement saved for the student; redirected to its page.</t>
+  </si>
+  <si>
+    <t>redirect=/student/placements/348812c8-3305-4981-badc-0215b55718d8; title=WIL 1; company=Test Host Company; required hours=320</t>
+  </si>
+  <si>
+    <t>evidence/system_test_run_2026-10-26.txt</t>
+  </si>
+  <si>
+    <t>TC-151</t>
+  </si>
+  <si>
+    <t>Placement validation</t>
+  </si>
+  <si>
+    <t>1. Send the form with 0, -10 and 6000 hours, no title, no company and no start date.</t>
+  </si>
+  <si>
+    <t>Invalid placement details</t>
+  </si>
+  <si>
+    <t>Each attempt rejected with a message; no placement saved.</t>
+  </si>
+  <si>
+    <t>0 hours -&gt; "Required hours must be a positive number."; -10 hours -&gt; "Required hours must be a positive number."; 6000 hours -&gt; "Required hours cannot be more than 5000."; no title -&gt; "Title, company and start date are required."; no company -&gt; "Title, company and start date are required."; no start date -&gt; "Title, company and start date are required."; extra placements saved: 0</t>
+  </si>
+  <si>
+    <t>TC-152</t>
+  </si>
+  <si>
+    <t>FR-03, FR-15</t>
+  </si>
+  <si>
+    <t>Edit a placement</t>
+  </si>
+  <si>
+    <t>TC-150 placement exists</t>
+  </si>
+  <si>
+    <t>1. Change own placement to 300 hours. 2. Try to edit Sihle's placement.</t>
+  </si>
+  <si>
+    <t>300 hours; placement-sihle-1</t>
+  </si>
+  <si>
+    <t>Own placement updated; the other student's placement is refused and unchanged.</t>
+  </si>
+  <si>
+    <t>own placement now 300 hours; editing Sihle's placement -&gt; "Placement not found."; Sihle's hours still 200</t>
+  </si>
+  <si>
+    <t>TC-153</t>
+  </si>
+  <si>
+    <t>FR-04, FR-15</t>
+  </si>
+  <si>
+    <t>Entry on another student's placement</t>
+  </si>
+  <si>
+    <t>1. Create an entry on Sihle's placement. 2. Create one on an unknown placement.</t>
+  </si>
+  <si>
+    <t>placement-sihle-1; no-such-placement</t>
+  </si>
+  <si>
+    <t>Both rejected with a message.</t>
+  </si>
+  <si>
+    <t>Sihle's placement -&gt; "Choose one of your WIL placements for this entry."; unknown placement -&gt; "Choose one of your WIL placements for this entry."</t>
+  </si>
+  <si>
+    <t>TC-154</t>
+  </si>
+  <si>
+    <t>Placement page access</t>
+  </si>
+  <si>
+    <t>1. Open Sihle's placement page. 2. Open own placement page.</t>
+  </si>
+  <si>
+    <t>placement-sihle-1; TC-150 placement</t>
+  </si>
+  <si>
+    <t>Other student's placement not shown; own placement shown.</t>
+  </si>
+  <si>
+    <t>Sihle's placement shown: false; own placement shown: true</t>
+  </si>
+  <si>
+    <t>TC-155</t>
+  </si>
+  <si>
+    <t>FR-10, FR-15</t>
+  </si>
+  <si>
+    <t>Hours per placement</t>
+  </si>
+  <si>
+    <t>Signed in as Dylan</t>
+  </si>
+  <si>
+    <t>1. Open My WIL placements.</t>
+  </si>
+  <si>
+    <t>Dylan's WIL 1 and WIL 2</t>
+  </si>
+  <si>
+    <t>Each placement shows its own verified hours against its own required hours.</t>
+  </si>
+  <si>
+    <t>WIL 1 120 of 120 shown: true; WIL 2 8 of 200 shown: true</t>
+  </si>
+  <si>
+    <t>TC-156</t>
+  </si>
+  <si>
+    <t>New entry and edit pages (DEF-06 retest)</t>
+  </si>
+  <si>
+    <t>Student with a placement</t>
+  </si>
+  <si>
+    <t>1. Open the new entry page. 2. Open the edit placement page.</t>
+  </si>
+  <si>
+    <t>TC-150 placement</t>
+  </si>
+  <si>
+    <t>Both pages load (200) and list the placement.</t>
+  </si>
+  <si>
+    <t>new entry page 200 (placement listed: true); edit page 200 (form shown: true)</t>
+  </si>
+  <si>
+    <t>TC-157</t>
+  </si>
+  <si>
+    <t>FR-16</t>
+  </si>
+  <si>
+    <t>Upload an MOU</t>
+  </si>
+  <si>
+    <t>1. Upload a PDF as the MOU.</t>
+  </si>
+  <si>
+    <t>Signed MOU.pdf</t>
+  </si>
+  <si>
+    <t>Saved under a random name; the original name is shown.</t>
+  </si>
+  <si>
+    <t>stored as fff02138-1706-4f5a-a87d-6bb5af3d95e2.pdf; file on disk: true; name shown to users "Signed MOU.pdf"</t>
+  </si>
+  <si>
+    <t>TC-158</t>
+  </si>
+  <si>
+    <t>Replace a document</t>
+  </si>
+  <si>
+    <t>TC-157 MOU exists</t>
+  </si>
+  <si>
+    <t>1. Upload another PDF as the MOU.</t>
+  </si>
+  <si>
+    <t>Signed MOU v2.pdf</t>
+  </si>
+  <si>
+    <t>Still one MOU; the old file is deleted.</t>
+  </si>
+  <si>
+    <t>MOU rows: 1; new file 303ca862-888c-47b7-ad65-d0b798b67e3f.pdf; old file removed: true</t>
+  </si>
+  <si>
+    <t>TC-159</t>
+  </si>
+  <si>
+    <t>Attendance register per semester</t>
+  </si>
+  <si>
+    <t>Placement that spans two semesters</t>
+  </si>
+  <si>
+    <t>1. Upload a register for the current semester twice and for the first semester once. 2. Try invalid semesters.</t>
+  </si>
+  <si>
+    <t>2026-S1, 2026-S2; 2026-S3, 2020-S1, 2099-S1, empty</t>
+  </si>
+  <si>
+    <t>One register per semester; invalid semesters rejected.</t>
+  </si>
+  <si>
+    <t>registers before: 0; after uploading 2026-S2 twice and 2026-S1 once: 2026-S1, 2026-S2; "2026-S3" -&gt; "Choose a semester between the placement start and now."; "2020-S1" -&gt; "Choose a semester between the placement start and now."; "2099-S1" -&gt; "Choose a semester between the placement start and now."; "" -&gt; "Choose a semester between the placement start and now."</t>
+  </si>
+  <si>
+    <t>TC-160</t>
+  </si>
+  <si>
+    <t>FR-16, NFR-03</t>
+  </si>
+  <si>
+    <t>Invalid or oversized documents</t>
+  </si>
+  <si>
+    <t>1. Upload an .exe, a program renamed to .pdf, a PNG renamed to .pdf, an empty file, a 10.5 MB PDF and an unknown document type.</t>
+  </si>
+  <si>
+    <t>Six invalid uploads</t>
+  </si>
+  <si>
+    <t>Every upload rejected with a message; nothing saved.</t>
+  </si>
+  <si>
+    <t>.exe file -&gt; "Documents must be PDF, PNG or JPG files."; program renamed to .pdf -&gt; "Documents must be PDF, PNG or JPG files."; PNG renamed to .pdf -&gt; "Documents must be PDF, PNG or JPG files."; empty file -&gt; "Choose a file to upload."; 10.5 MB PDF -&gt; "The file is larger than 10 MB."; unknown document type -&gt; "Choose which document you are uploading."; code of conduct rows saved: 0</t>
+  </si>
+  <si>
+    <t>TC-161</t>
+  </si>
+  <si>
+    <t>FR-03, FR-16</t>
+  </si>
+  <si>
+    <t>Upload to another placement</t>
+  </si>
+  <si>
+    <t>Signed in as a new student; coordinator</t>
+  </si>
+  <si>
+    <t>1. Upload to Sihle's placement as another student. 2. Upload as the coordinator.</t>
+  </si>
+  <si>
+    <t>placement-sihle-1</t>
+  </si>
+  <si>
+    <t>Both refused; nothing saved.</t>
+  </si>
+  <si>
+    <t>other student's placement -&gt; "Placement not found."; coordinator upload accepted: false; letters on Sihle's placement: 0</t>
+  </si>
+  <si>
+    <t>TC-162</t>
+  </si>
+  <si>
+    <t>Document download access</t>
+  </si>
+  <si>
+    <t>TC-158 MOU exists</t>
+  </si>
+  <si>
+    <t>1. Download as the owner, another student, signed out, the coordinator and the lecturer. 2. Request an unknown id.</t>
+  </si>
+  <si>
+    <t>Document id</t>
+  </si>
+  <si>
+    <t>200 for the owner and staff (PDF), 403 for another student, 401 signed out, 404 for an unknown id.</t>
+  </si>
+  <si>
+    <t>owner 200 (application/pdf); other student 403; signed out 401; coordinator 200; lecturer 200; unknown id 404</t>
+  </si>
+  <si>
+    <t>TC-163</t>
+  </si>
+  <si>
+    <t>Remove a document</t>
+  </si>
+  <si>
+    <t>1. Remove it as another student. 2. Remove it as the owner.</t>
+  </si>
+  <si>
+    <t>Other student refused; the owner removes the record and the file.</t>
+  </si>
+  <si>
+    <t>other student -&gt; "Document not found." (document kept: true); owner -&gt; row and file removed: true</t>
+  </si>
+  <si>
+    <t>TC-164</t>
+  </si>
+  <si>
+    <t>Document status on pages</t>
+  </si>
+  <si>
+    <t>1. Open Dylan's WIL 2, Sihle's WIL 1 and Dylan's placements.</t>
+  </si>
+  <si>
+    <t>Seeded documents</t>
+  </si>
+  <si>
+    <t>Uploaded and Missing shown correctly; the card shows documents 3 of 3.</t>
+  </si>
+  <si>
+    <t>Dylan WIL 2 complete (no Missing): true; Sihle shows Uploaded and Missing: true; placement card shows documents 3 of 3: true</t>
+  </si>
+  <si>
+    <t>TC-165</t>
+  </si>
+  <si>
+    <t>FR-16, NFR-02</t>
+  </si>
+  <si>
+    <t>Large document upload</t>
+  </si>
+  <si>
+    <t>1. Upload a 9.5 MB PDF through the student page.</t>
+  </si>
+  <si>
+    <t>9.5 MB PDF</t>
+  </si>
+  <si>
+    <t>Accepted; the stored size matches.</t>
+  </si>
+  <si>
+    <t>response: success; stored size 9961479 of 9961479 bytes</t>
+  </si>
+  <si>
+    <t>TC-166</t>
+  </si>
+  <si>
+    <t>FR-17</t>
+  </si>
+  <si>
+    <t>Coordinator opens a student profile</t>
+  </si>
+  <si>
+    <t>1. Open Dylan's profile.</t>
+  </si>
+  <si>
+    <t>student-1</t>
+  </si>
+  <si>
+    <t>Both placements, logbook entries and document links shown; no upload, replace or remove buttons.</t>
+  </si>
+  <si>
+    <t>status 200; both placements: true; logbook entry shown: true; document link shown: true; read-only (no upload/replace/remove): true</t>
+  </si>
+  <si>
+    <t>TC-167</t>
+  </si>
+  <si>
+    <t>Lecturer opens a student profile</t>
+  </si>
+  <si>
+    <t>1. Open Sihle's profile.</t>
+  </si>
+  <si>
+    <t>student-2</t>
+  </si>
+  <si>
+    <t>Profile shown.</t>
+  </si>
+  <si>
+    <t>status 200; shows Sihle and her placement: true</t>
+  </si>
+  <si>
+    <t>TC-168</t>
+  </si>
+  <si>
+    <t>FR-03, FR-17</t>
+  </si>
+  <si>
+    <t>Profile blocked for students</t>
+  </si>
+  <si>
+    <t>Redirected; none of Dylan's data in the response.</t>
+  </si>
+  <si>
+    <t>status 307; Dylan's placement in the response to Sihle: false</t>
+  </si>
+  <si>
+    <t>TC-169</t>
+  </si>
+  <si>
+    <t>Unknown or staff profile</t>
+  </si>
+  <si>
+    <t>1. Open the profile of the coordinator account and of an unknown id.</t>
+  </si>
+  <si>
+    <t>coordinator-1; no-such-student</t>
+  </si>
+  <si>
+    <t>404 Not Found for both.</t>
+  </si>
+  <si>
+    <t>coordinator account -&gt; 404; unknown id -&gt; 404</t>
+  </si>
+  <si>
+    <t>TC-170</t>
+  </si>
+  <si>
+    <t>FR-11, FR-17</t>
+  </si>
+  <si>
+    <t>Dashboard links and missing documents</t>
+  </si>
+  <si>
+    <t>1. Open the dashboard.</t>
+  </si>
+  <si>
+    <t>Each student links to their profile; missing documents are shown.</t>
+  </si>
+  <si>
+    <t>profile links: true; Moe row shows missing: true; Sihle row shows missing: true</t>
+  </si>
+  <si>
+    <t>TC-171</t>
+  </si>
+  <si>
+    <t>Blocked pages send no data (DEF-07 retest)</t>
+  </si>
+  <si>
+    <t>DEF-07 fix deployed</t>
+  </si>
+  <si>
+    <t>1. Request staff pages as a student and with a made-up cookie. 2. Request a student page as the coordinator.</t>
+  </si>
+  <si>
+    <t>Five requests</t>
+  </si>
+  <si>
+    <t>Each is redirected and none of the page's data is in the response.</t>
+  </si>
+  <si>
+    <t>student -&gt; /coordinator: 307, leaked nothing; made-up cookie -&gt; /coordinator: 307, leaked nothing; student -&gt; another student's profile: 307, leaked nothing; made-up cookie -&gt; student profile: 307, leaked nothing; coordinator -&gt; a student's placement page: 307, leaked nothing</t>
+  </si>
+  <si>
+    <t>TC-172</t>
+  </si>
+  <si>
+    <t>FR-18</t>
+  </si>
+  <si>
+    <t>Automatic WIL completion</t>
+  </si>
+  <si>
+    <t>Student with a 4-hour placement</t>
+  </si>
+  <si>
+    <t>1. Add a 4-hour entry, submit it and approve it as the mentor. 2. Open the placement, the dashboard and Dylan's profile.</t>
+  </si>
+  <si>
+    <t>4-hour placement</t>
+  </si>
+  <si>
+    <t>Placement marked WIL completed after approval; New entry hidden; Lerato shown as WIL completed.</t>
+  </si>
+  <si>
+    <t>4-hour placement before approval completed: false; after approval: true (New entry button hidden: true); Lerato on dashboard: WIL completed; Dylan's profile marks WIL 1 completed: true</t>
+  </si>
+  <si>
+    <t>TC-173</t>
+  </si>
+  <si>
+    <t>Completed placement is locked</t>
+  </si>
+  <si>
+    <t>TC-172 placement completed</t>
+  </si>
+  <si>
+    <t>1. Try a new entry, submitting a draft, uploading, editing, and removing a document of Dylan's WIL 1.</t>
+  </si>
+  <si>
+    <t>Completed placements</t>
+  </si>
+  <si>
+    <t>Every change refused with the locked message; nothing changed.</t>
+  </si>
+  <si>
+    <t>new entry -&gt; "This WIL placement is completed and locked. Add a new placement to continue."; submit remaining draft -&gt; "This WIL placement is completed and locked. Add a new placement to continue."; upload document -&gt; "This WIL placement is completed and locked. Add a new placement to continue."; edit placement -&gt; "This WIL placement is completed and locked. Add a new placement to continue."; remove document (Dylan, WIL 1) -&gt; "This WIL placement is completed and locked. Add a new placement to continue."; entries still 2; draft still draft; required hours still 4; Dylan's MOU kept: true</t>
+  </si>
+  <si>
+    <t>TC-174</t>
+  </si>
+  <si>
+    <t>FR-11, FR-15</t>
+  </si>
+  <si>
+    <t>No placement status</t>
+  </si>
+  <si>
+    <t>New sign-up</t>
+  </si>
+  <si>
+    <t>1. Open the dashboard. 2. Add a placement that starts today. 3. Open the dashboard again.</t>
+  </si>
+  <si>
+    <t>Fresh Student</t>
+  </si>
+  <si>
+    <t>No placement, then On track.</t>
+  </si>
+  <si>
+    <t>before adding a placement: No placement; after adding one that starts today: On track</t>
+  </si>
+  <si>
+    <t>TC-175</t>
+  </si>
+  <si>
+    <t>Demo accounts listed (DEF-05 retest)</t>
+  </si>
+  <si>
+    <t>App running</t>
+  </si>
+  <si>
+    <t>1. Open the sign-in page.</t>
+  </si>
+  <si>
+    <t>All five demo accounts are listed.</t>
+  </si>
+  <si>
+    <t>listed 5 of 5: student1@ctucareer.co.za, student2@ctucareer.co.za, student3@ctucareer.co.za, coordinator@ctucareer.co.za, lecturer@ctucareer.co.za</t>
+  </si>
+  <si>
+    <t>Redirected to /coordinator; no student page content in the response.</t>
+  </si>
+  <si>
+    <t>status 307; redirected to /coordinator: true; student page content in response: false</t>
+  </si>
+  <si>
+    <t>Redirected to /student; no dashboard content in the response.</t>
+  </si>
+  <si>
+    <t>status 307; redirected to /student: true; dashboard content in response: false</t>
+  </si>
+  <si>
+    <t>Both rejected; no dashboard content in the response.</t>
+  </si>
+  <si>
+    <t>unsigned 'coordinator-1' -&gt; status 307, dashboard content in response: false; another user's signature -&gt; status 307, dashboard content in response: false</t>
+  </si>
+  <si>
+    <t>Placement logbook view</t>
+  </si>
+  <si>
+    <t>1. Open /student/placements/placement-sihle-1.</t>
+  </si>
+  <si>
+    <t>Statuses shown; 'X of 200 verified hours completed' correct for the placement.</t>
+  </si>
+  <si>
+    <t>1. Insert eleven kinds of invalid rows.</t>
+  </si>
+  <si>
+    <t>Hours 30, bad status, entry for a missing placement, placement with 0 hours, placement for a missing student, bad role, duplicate email, unknown document type, register without a semester, second MOU, token without decision</t>
+  </si>
+  <si>
+    <t>hours = 30: rejected (CHECK constraint failed); unknown status: rejected (CHECK constraint failed); entry for missing placement: rejected (FOREIGN KEY constraint failed); placement with 0 required hours: rejected (CHECK constraint failed); placement for missing student: rejected (FOREIGN KEY constraint failed); unknown role: rejected (CHECK constraint failed); duplicate email (case): rejected (UNIQUE constraint failed); document with an unknown type: rejected (CHECK constraint failed); attendance register without a semester: rejected (CHECK constraint failed); second MOU for one placement: rejected (UNIQUE constraint failed); token used without decision: rejected (CHECK constraint failed)</t>
+  </si>
+  <si>
+    <t>1. Request seven pages 10 times each. 2. Time one entry creation.</t>
+  </si>
+  <si>
+    <t>/, /student, placement logbook, /student/entries/new, /coordinator, student profile, /verify/&lt;token&gt;</t>
+  </si>
+  <si>
+    <t>Every response under 2 seconds and no page errors.</t>
+  </si>
+  <si>
+    <t>/ avg 3 ms, max 5 ms; /student avg 4 ms, max 4 ms; /student/placements/placement-sihle-1 avg 5 ms, max 7 ms; /student/entries/new avg 4 ms, max 4 ms; /coordinator avg 5 ms, max 7 ms; /coordinator/students/student-1 avg 5 ms, max 5 ms; /verify/&lt;token&gt; avg 3 ms, max 5 ms; create entry 10 ms; pages with errors: none</t>
+  </si>
+  <si>
+    <t>Seed data contains only the four team members, one synthetic student (Lerato Mokoena), a synthetic coordinator and a synthetic lecturer, invented entries and placements, and synthetic demo PDFs marked as demonstration data; no other personal data is stored.</t>
+  </si>
+  <si>
+    <t>database/seed.sql; database/demo-documents</t>
   </si>
 </sst>
 </file>
@@ -1420,7 +1960,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1452,8 +1992,14 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1759,7 +2305,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L58"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1776,20 +2322,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -2665,7 +3211,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>175</v>
       </c>
@@ -2685,48 +3231,48 @@
         <v>179</v>
       </c>
       <c r="G26" s="8" t="s">
+        <v>579</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="K26" s="9">
+        <v>46321</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
         <v>180</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="K26" s="9">
-        <v>46318</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
-        <v>182</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>168</v>
       </c>
       <c r="C27" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E27" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="F27" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="E27" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>186</v>
-      </c>
       <c r="G27" s="8" t="s">
-        <v>187</v>
+        <v>581</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>188</v>
+        <v>582</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>20</v>
@@ -2735,36 +3281,36 @@
         <v>123</v>
       </c>
       <c r="K27" s="9">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>124</v>
+        <v>409</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>168</v>
       </c>
       <c r="C28" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="G28" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="H28" s="8" t="s">
         <v>191</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>195</v>
       </c>
       <c r="I28" s="8" t="s">
         <v>20</v>
@@ -2781,28 +3327,28 @@
     </row>
     <row r="29" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>168</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>20</v>
@@ -2817,30 +3363,30 @@
         <v>124</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="E30" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="F30" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>206</v>
-      </c>
       <c r="G30" s="8" t="s">
-        <v>207</v>
+        <v>583</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>208</v>
+        <v>584</v>
       </c>
       <c r="I30" s="8" t="s">
         <v>20</v>
@@ -2849,36 +3395,36 @@
         <v>123</v>
       </c>
       <c r="K30" s="9">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="L30" s="8" t="s">
-        <v>124</v>
+        <v>409</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>110</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>20</v>
@@ -2895,28 +3441,28 @@
     </row>
     <row r="32" spans="1:12" ht="165" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>110</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="I32" s="8" t="s">
         <v>20</v>
@@ -2933,28 +3479,28 @@
     </row>
     <row r="33" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="H33" s="8" t="s">
         <v>221</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>227</v>
       </c>
       <c r="I33" s="8" t="s">
         <v>20</v>
@@ -2971,28 +3517,28 @@
     </row>
     <row r="34" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="I34" s="8" t="s">
         <v>20</v>
@@ -3009,28 +3555,28 @@
     </row>
     <row r="35" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="G35" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="H35" s="8" t="s">
         <v>235</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>241</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>20</v>
@@ -3047,28 +3593,28 @@
     </row>
     <row r="36" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="G36" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="H36" s="8" t="s">
         <v>243</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>249</v>
       </c>
       <c r="I36" s="8" t="s">
         <v>20</v>
@@ -3085,28 +3631,28 @@
     </row>
     <row r="37" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>20</v>
@@ -3123,28 +3669,28 @@
     </row>
     <row r="38" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="H38" s="8" t="s">
         <v>256</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>262</v>
       </c>
       <c r="I38" s="8" t="s">
         <v>20</v>
@@ -3161,28 +3707,28 @@
     </row>
     <row r="39" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="G39" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="H39" s="8" t="s">
         <v>264</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="H39" s="8" t="s">
-        <v>270</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>20</v>
@@ -3199,28 +3745,28 @@
     </row>
     <row r="40" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="H40" s="8" t="s">
         <v>271</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>277</v>
       </c>
       <c r="I40" s="8" t="s">
         <v>20</v>
@@ -3237,28 +3783,28 @@
     </row>
     <row r="41" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="G41" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="H41" s="8" t="s">
         <v>279</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="H41" s="8" t="s">
-        <v>285</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>20</v>
@@ -3275,28 +3821,28 @@
     </row>
     <row r="42" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="G42" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="H42" s="8" t="s">
         <v>287</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>293</v>
       </c>
       <c r="I42" s="8" t="s">
         <v>20</v>
@@ -3313,28 +3859,28 @@
     </row>
     <row r="43" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="H43" s="8" t="s">
         <v>294</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>300</v>
       </c>
       <c r="I43" s="8" t="s">
         <v>20</v>
@@ -3351,28 +3897,28 @@
     </row>
     <row r="44" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="H44" s="8" t="s">
         <v>301</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>307</v>
       </c>
       <c r="I44" s="8" t="s">
         <v>20</v>
@@ -3389,28 +3935,28 @@
     </row>
     <row r="45" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="G45" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="H45" s="8" t="s">
         <v>309</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>315</v>
       </c>
       <c r="I45" s="8" t="s">
         <v>20</v>
@@ -3427,28 +3973,28 @@
     </row>
     <row r="46" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="G46" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="H46" s="8" t="s">
         <v>317</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H46" s="8" t="s">
-        <v>323</v>
       </c>
       <c r="I46" s="8" t="s">
         <v>20</v>
@@ -3465,28 +4011,28 @@
     </row>
     <row r="47" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B47" s="8" t="s">
         <v>109</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>325</v>
+        <v>585</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>178</v>
+        <v>586</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>327</v>
+        <v>587</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="I47" s="8" t="s">
         <v>20</v>
@@ -3495,36 +4041,36 @@
         <v>123</v>
       </c>
       <c r="K47" s="9">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="L47" s="8" t="s">
-        <v>124</v>
+        <v>409</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>113</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="I48" s="8" t="s">
         <v>20</v>
@@ -3541,28 +4087,28 @@
     </row>
     <row r="49" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="I49" s="8" t="s">
         <v>20</v>
@@ -3579,28 +4125,28 @@
     </row>
     <row r="50" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>112</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="D50" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="F50" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="E50" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>186</v>
-      </c>
       <c r="G50" s="8" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="I50" s="8" t="s">
         <v>20</v>
@@ -3617,28 +4163,28 @@
     </row>
     <row r="51" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>162</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="I51" s="8" t="s">
         <v>20</v>
@@ -3653,68 +4199,68 @@
         <v>124</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="180" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" ht="375" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>588</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>589</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>590</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J52" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="K52" s="9">
+        <v>46321</v>
+      </c>
+      <c r="L52" s="8" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="180" x14ac:dyDescent="0.25">
+      <c r="A53" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="D53" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="B52" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="G52" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="H52" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="I52" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J52" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="K52" s="9">
-        <v>46318</v>
-      </c>
-      <c r="L52" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="105" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="B53" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>366</v>
-      </c>
       <c r="E53" s="8" t="s">
-        <v>367</v>
+        <v>591</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>368</v>
+        <v>592</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>369</v>
+        <v>593</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>370</v>
+        <v>594</v>
       </c>
       <c r="I53" s="8" t="s">
         <v>20</v>
@@ -3723,36 +4269,36 @@
         <v>123</v>
       </c>
       <c r="K53" s="9">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="L53" s="8" t="s">
-        <v>124</v>
+        <v>409</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="I54" s="8" t="s">
         <v>20</v>
@@ -3764,33 +4310,33 @@
         <v>46318</v>
       </c>
       <c r="L54" s="8" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="I55" s="8" t="s">
         <v>20</v>
@@ -3802,33 +4348,33 @@
         <v>46318</v>
       </c>
       <c r="L55" s="8" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="I56" s="8" t="s">
         <v>20</v>
@@ -3840,33 +4386,33 @@
         <v>46318</v>
       </c>
       <c r="L56" s="8" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="150" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>405</v>
+        <v>595</v>
       </c>
       <c r="I57" s="8" t="s">
         <v>20</v>
@@ -3875,52 +4421,1040 @@
         <v>123</v>
       </c>
       <c r="K57" s="9">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="L57" s="8" t="s">
-        <v>403</v>
+        <v>596</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="I58" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="J58" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="K58" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="L58" s="10" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A59" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="F59" s="11" t="s">
         <v>406</v>
       </c>
-      <c r="B58" s="10" t="s">
+      <c r="G59" s="11" t="s">
         <v>407</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="H59" s="11" t="s">
         <v>408</v>
       </c>
-      <c r="D58" s="10" t="s">
+      <c r="I59" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J59" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K59" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L59" s="11" t="s">
         <v>409</v>
       </c>
-      <c r="E58" s="10" t="s">
+    </row>
+    <row r="60" spans="1:12" ht="195" x14ac:dyDescent="0.25">
+      <c r="A60" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="F58" s="10" t="s">
+      <c r="B60" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="C60" s="11" t="s">
         <v>411</v>
       </c>
-      <c r="G58" s="10" t="s">
+      <c r="D60" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="E60" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="H58" s="10" t="s">
+      <c r="F60" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="I58" s="10" t="s">
+      <c r="G60" s="11" t="s">
         <v>414</v>
       </c>
-      <c r="J58" s="10" t="s">
+      <c r="H60" s="11" t="s">
         <v>415</v>
       </c>
-      <c r="K58" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="L58" s="10" t="s">
+      <c r="I60" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J60" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K60" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L60" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A61" s="11" t="s">
         <v>416</v>
       </c>
+      <c r="B61" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>419</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="F61" s="11" t="s">
+        <v>421</v>
+      </c>
+      <c r="G61" s="11" t="s">
+        <v>422</v>
+      </c>
+      <c r="H61" s="11" t="s">
+        <v>423</v>
+      </c>
+      <c r="I61" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J61" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K61" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L61" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A62" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="F62" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="G62" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="H62" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="I62" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J62" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K62" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L62" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="F63" s="11" t="s">
+        <v>434</v>
+      </c>
+      <c r="G63" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="H63" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="I63" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J63" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K63" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L63" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A64" s="11" t="s">
+        <v>437</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>439</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>441</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="G64" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="H64" s="11" t="s">
+        <v>444</v>
+      </c>
+      <c r="I64" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J64" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K64" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L64" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A65" s="11" t="s">
+        <v>445</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>446</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>447</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>448</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>449</v>
+      </c>
+      <c r="G65" s="11" t="s">
+        <v>450</v>
+      </c>
+      <c r="H65" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="I65" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J65" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K65" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L65" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A66" s="11" t="s">
+        <v>452</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>453</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>447</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="F66" s="11" t="s">
+        <v>456</v>
+      </c>
+      <c r="G66" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="H66" s="11" t="s">
+        <v>458</v>
+      </c>
+      <c r="I66" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J66" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K66" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L66" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A67" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>453</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>460</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>461</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="F67" s="11" t="s">
+        <v>463</v>
+      </c>
+      <c r="G67" s="11" t="s">
+        <v>464</v>
+      </c>
+      <c r="H67" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="I67" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J67" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K67" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L67" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="210" x14ac:dyDescent="0.25">
+      <c r="A68" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>453</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="F68" s="11" t="s">
+        <v>470</v>
+      </c>
+      <c r="G68" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="H68" s="11" t="s">
+        <v>472</v>
+      </c>
+      <c r="I68" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J68" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K68" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L68" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="210" x14ac:dyDescent="0.25">
+      <c r="A69" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>447</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="F69" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="G69" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="H69" s="11" t="s">
+        <v>479</v>
+      </c>
+      <c r="I69" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J69" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K69" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L69" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A70" s="11" t="s">
+        <v>480</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>481</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>482</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>483</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>484</v>
+      </c>
+      <c r="F70" s="11" t="s">
+        <v>485</v>
+      </c>
+      <c r="G70" s="11" t="s">
+        <v>486</v>
+      </c>
+      <c r="H70" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="I70" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J70" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K70" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L70" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A71" s="11" t="s">
+        <v>488</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>489</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>491</v>
+      </c>
+      <c r="F71" s="11" t="s">
+        <v>492</v>
+      </c>
+      <c r="G71" s="11" t="s">
+        <v>493</v>
+      </c>
+      <c r="H71" s="11" t="s">
+        <v>494</v>
+      </c>
+      <c r="I71" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J71" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K71" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L71" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A72" s="11" t="s">
+        <v>495</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>453</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="E72" s="11" t="s">
+        <v>497</v>
+      </c>
+      <c r="F72" s="11" t="s">
+        <v>492</v>
+      </c>
+      <c r="G72" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="H72" s="11" t="s">
+        <v>499</v>
+      </c>
+      <c r="I72" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J72" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K72" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L72" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A73" s="11" t="s">
+        <v>500</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>453</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>501</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>502</v>
+      </c>
+      <c r="F73" s="11" t="s">
+        <v>503</v>
+      </c>
+      <c r="G73" s="11" t="s">
+        <v>504</v>
+      </c>
+      <c r="H73" s="11" t="s">
+        <v>505</v>
+      </c>
+      <c r="I73" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J73" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K73" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L73" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A74" s="11" t="s">
+        <v>506</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>507</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>447</v>
+      </c>
+      <c r="E74" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="F74" s="11" t="s">
+        <v>510</v>
+      </c>
+      <c r="G74" s="11" t="s">
+        <v>511</v>
+      </c>
+      <c r="H74" s="11" t="s">
+        <v>512</v>
+      </c>
+      <c r="I74" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J74" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K74" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L74" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A75" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>515</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>516</v>
+      </c>
+      <c r="F75" s="11" t="s">
+        <v>517</v>
+      </c>
+      <c r="G75" s="11" t="s">
+        <v>518</v>
+      </c>
+      <c r="H75" s="11" t="s">
+        <v>519</v>
+      </c>
+      <c r="I75" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J75" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K75" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L75" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A76" s="11" t="s">
+        <v>520</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>522</v>
+      </c>
+      <c r="F76" s="11" t="s">
+        <v>523</v>
+      </c>
+      <c r="G76" s="11" t="s">
+        <v>524</v>
+      </c>
+      <c r="H76" s="11" t="s">
+        <v>525</v>
+      </c>
+      <c r="I76" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J76" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K76" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L76" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A77" s="11" t="s">
+        <v>526</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>527</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>528</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>516</v>
+      </c>
+      <c r="F77" s="11" t="s">
+        <v>517</v>
+      </c>
+      <c r="G77" s="11" t="s">
+        <v>529</v>
+      </c>
+      <c r="H77" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="I77" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J77" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K77" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L77" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A78" s="11" t="s">
+        <v>531</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>532</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="E78" s="11" t="s">
+        <v>533</v>
+      </c>
+      <c r="F78" s="11" t="s">
+        <v>534</v>
+      </c>
+      <c r="G78" s="11" t="s">
+        <v>535</v>
+      </c>
+      <c r="H78" s="11" t="s">
+        <v>536</v>
+      </c>
+      <c r="I78" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J78" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K78" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L78" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A79" s="11" t="s">
+        <v>537</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>538</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>539</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="E79" s="11" t="s">
+        <v>540</v>
+      </c>
+      <c r="F79" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="G79" s="11" t="s">
+        <v>541</v>
+      </c>
+      <c r="H79" s="11" t="s">
+        <v>542</v>
+      </c>
+      <c r="I79" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J79" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K79" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L79" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="150" x14ac:dyDescent="0.25">
+      <c r="A80" s="11" t="s">
+        <v>543</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>544</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>545</v>
+      </c>
+      <c r="E80" s="11" t="s">
+        <v>546</v>
+      </c>
+      <c r="F80" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="G80" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="H80" s="11" t="s">
+        <v>549</v>
+      </c>
+      <c r="I80" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J80" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K80" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L80" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A81" s="11" t="s">
+        <v>550</v>
+      </c>
+      <c r="B81" s="11" t="s">
+        <v>551</v>
+      </c>
+      <c r="C81" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="D81" s="11" t="s">
+        <v>553</v>
+      </c>
+      <c r="E81" s="11" t="s">
+        <v>554</v>
+      </c>
+      <c r="F81" s="11" t="s">
+        <v>555</v>
+      </c>
+      <c r="G81" s="11" t="s">
+        <v>556</v>
+      </c>
+      <c r="H81" s="11" t="s">
+        <v>557</v>
+      </c>
+      <c r="I81" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J81" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K81" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L81" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="315" x14ac:dyDescent="0.25">
+      <c r="A82" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>551</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>559</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>560</v>
+      </c>
+      <c r="E82" s="11" t="s">
+        <v>561</v>
+      </c>
+      <c r="F82" s="11" t="s">
+        <v>562</v>
+      </c>
+      <c r="G82" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="H82" s="11" t="s">
+        <v>564</v>
+      </c>
+      <c r="I82" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J82" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K82" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L82" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A83" s="11" t="s">
+        <v>565</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>566</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="E83" s="11" t="s">
+        <v>569</v>
+      </c>
+      <c r="F83" s="11" t="s">
+        <v>570</v>
+      </c>
+      <c r="G83" s="11" t="s">
+        <v>571</v>
+      </c>
+      <c r="H83" s="11" t="s">
+        <v>572</v>
+      </c>
+      <c r="I83" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J83" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K83" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L83" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A84" s="11" t="s">
+        <v>573</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C84" s="11" t="s">
+        <v>574</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>575</v>
+      </c>
+      <c r="E84" s="11" t="s">
+        <v>576</v>
+      </c>
+      <c r="F84" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="G84" s="11" t="s">
+        <v>577</v>
+      </c>
+      <c r="H84" s="11" t="s">
+        <v>578</v>
+      </c>
+      <c r="I84" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J84" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K84" s="14">
+        <v>46321</v>
+      </c>
+      <c r="L84" s="11" t="s">
+        <v>409</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L100" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:L126" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
